--- a/artfynd/A 52462-2019 artfynd.xlsx
+++ b/artfynd/A 52462-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120977832</v>
       </c>
       <c r="B2" t="n">
-        <v>57295</v>
+        <v>57298</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52462-2019 artfynd.xlsx
+++ b/artfynd/A 52462-2019 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>120977832</v>
       </c>
       <c r="B2" t="n">
-        <v>57298</v>
+        <v>57302</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 52462-2019 artfynd.xlsx
+++ b/artfynd/A 52462-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120977832</v>
       </c>
       <c r="B2" t="n">
-        <v>57302</v>
+        <v>57303</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52462-2019 artfynd.xlsx
+++ b/artfynd/A 52462-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120977832</v>
       </c>
       <c r="B2" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
